--- a/results.xlsx
+++ b/results.xlsx
@@ -576,29 +576,21 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Retour au portail Retour Liste Retour Formulaire</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Aide</t>
-        </is>
-      </c>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1730599380363 59</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Retour au portail Retour Liste Retour Formulaire</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Aide</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
@@ -643,7 +635,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>08/05/2027</t>
+          <t>22/05/2027</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -681,29 +673,21 @@
       <c r="AC2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Retour au portail Retour Liste Retour Formulaire</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Aide</t>
-        </is>
-      </c>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1730599380363 59</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Retour au portail Retour Liste Retour Formulaire</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Aide</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
@@ -786,29 +770,21 @@
       <c r="AC3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Retour au portail Retour Liste Retour Formulaire</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Aide</t>
-        </is>
-      </c>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1731099333116 50</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Retour au portail Retour Liste Retour Formulaire</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Aide</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
@@ -903,29 +879,21 @@
       <c r="AC4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Retour au portail Retour Liste Retour Formulaire</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Aide</t>
-        </is>
-      </c>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1751199410083 19</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Retour au portail Retour Liste Retour Formulaire</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Aide</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
@@ -1020,29 +988,21 @@
       <c r="AC5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Retour au portail Retour Liste Retour Formulaire</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Aide</t>
-        </is>
-      </c>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1751199410083 19</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Retour au portail Retour Liste Retour Formulaire</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Aide</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
@@ -1133,29 +1093,21 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Retour au portail Retour Liste Retour Formulaire</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Aide</t>
-        </is>
-      </c>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1761299350521 87</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Retour au portail Retour Liste Retour Formulaire</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Aide</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
@@ -1250,29 +1202,21 @@
       <c r="AC7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Retour au portail Retour Liste Retour Formulaire</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Aide</t>
-        </is>
-      </c>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1761299350521 87</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Retour au portail Retour Liste Retour Formulaire</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Aide</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
@@ -1355,29 +1299,21 @@
       <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Retour au portail Retour Liste Retour Formulaire</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Aide</t>
-        </is>
-      </c>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1761299350521 87</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Retour au portail Retour Liste Retour Formulaire</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Aide</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
@@ -1460,29 +1396,21 @@
       <c r="AC9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Retour au portail Retour Liste Retour Formulaire</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Aide</t>
-        </is>
-      </c>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1761299350521 87</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Retour au portail Retour Liste Retour Formulaire</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Aide</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
@@ -1565,29 +1493,21 @@
       <c r="AC10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Retour au portail Retour Liste Retour Formulaire</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Les informations ETM et MTM ne sont applicables que dans la période d'ouverture des droits de base AMO Aide</t>
-        </is>
-      </c>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1800599151054 08</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Retour au portail Retour Liste Retour Formulaire</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Les informations ETM et MTM ne sont applicables que dans la période d'ouverture des droits de base AMO Aide</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
@@ -1678,29 +1598,21 @@
       <c r="AC11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Retour au portail Retour Liste Retour Formulaire</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Aide</t>
-        </is>
-      </c>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1800599151054 08</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Retour au portail Retour Liste Retour Formulaire</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Aide</t>
-        </is>
-      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
@@ -1795,29 +1707,21 @@
       <c r="AC12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Retour au portail Retour Liste Retour Formulaire</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Aide</t>
-        </is>
-      </c>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1860199380206 97</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Retour au portail Retour Liste Retour Formulaire</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Aide</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
@@ -1908,29 +1812,21 @@
       <c r="AC13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Retour au portail Retour Liste Retour Formulaire</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Aide</t>
-        </is>
-      </c>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1860199380206 97</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Retour au portail Retour Liste Retour Formulaire</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Aide</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
@@ -2009,29 +1905,21 @@
       <c r="AC14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Retour au portail Retour Liste Retour Formulaire</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Les informations ETM et MTM ne sont applicables que dans la période d'ouverture des droits de base AMO Aide</t>
-        </is>
-      </c>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1860199380206 97</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Retour au portail Retour Liste Retour Formulaire</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Les informations ETM et MTM ne sont applicables que dans la période d'ouverture des droits de base AMO Aide</t>
-        </is>
-      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
